--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
